--- a/liste groupe Samedi.xlsx
+++ b/liste groupe Samedi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54543A7A-04F3-43B2-80E1-5E603426F06B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C712F1DA-7036-4AA2-9C92-A70AF0D88AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe Samedi.xlsx
+++ b/liste groupe Samedi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C712F1DA-7036-4AA2-9C92-A70AF0D88AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C292F8AD-43D5-4F1B-8D2A-BFA1B1105B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe Samedi.xlsx
+++ b/liste groupe Samedi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C292F8AD-43D5-4F1B-8D2A-BFA1B1105B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11557788-53F1-425E-9769-7825CF581BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe Samedi.xlsx
+++ b/liste groupe Samedi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11557788-53F1-425E-9769-7825CF581BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EED9112-EC75-4CEA-9683-11B02F4375E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe Samedi.xlsx
+++ b/liste groupe Samedi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EED9112-EC75-4CEA-9683-11B02F4375E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53FB61B5-4CAD-4B80-A678-F2C86A36FE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe Samedi.xlsx
+++ b/liste groupe Samedi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53FB61B5-4CAD-4B80-A678-F2C86A36FE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F4D151-44BE-41D9-8E39-F5323FACF492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe Samedi.xlsx
+++ b/liste groupe Samedi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F4D151-44BE-41D9-8E39-F5323FACF492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E77FA7-881E-4C46-BD9D-781CCFFC7D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6960" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
